--- a/asx_eod_output/Report_XLSX/Report_20260811.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260811.xlsx
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.345</v>
+        <v>2.335</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>164150</v>
+        <v>163450</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-350</v>
+        <v>-1050</v>
       </c>
     </row>
     <row r="6">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>64.29000000000001</v>
+        <v>64.27</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>711368.85</v>
+        <v>711147.55</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8520.049999999999</v>
+        <v>8298.75</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>174</v>
+        <v>173.9</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.37</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -650,24 +650,24 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.915</v>
+        <v>0.92</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9150</v>
+        <v>9200</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>138.64</v>
+        <v>138.34</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4.17</v>
+        <v>3.87</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>2.88%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>554560</v>
+        <v>553360</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>16680</v>
+        <v>15480</v>
       </c>
     </row>
     <row r="12">
@@ -758,24 +758,24 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.25%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
         <v>9412</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>988.26</v>
+        <v>941.2</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>75.3</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="15">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>35.6</v>
+        <v>35.55</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>32.91</v>
+        <v>32.94</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.62%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>42388.08</v>
+        <v>42426.72</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1442.56</v>
+        <v>1481.2</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1803095.73</v>
+        <v>1801016.01</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>28010.54</v>
+        <v>25930.82</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260811.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260811.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.602</v>
+        <v>1.622</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.027</v>
+        <v>0.047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>245395.96</v>
+        <v>248459.58</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>4135.89</v>
+        <v>7199.51</v>
       </c>
     </row>
     <row r="5">
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.335</v>
+        <v>2.34</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.015</v>
+        <v>-0.01</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>163450</v>
+        <v>163800</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-1050</v>
+        <v>-700</v>
       </c>
     </row>
     <row r="6">
@@ -542,24 +542,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.195</v>
+        <v>1.19</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.025</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>57458</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>68662.31</v>
+        <v>68375.02</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1149.16</v>
+        <v>-1436.45</v>
       </c>
     </row>
     <row r="7">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>64.27</v>
+        <v>64.19</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>711147.55</v>
+        <v>710262.35</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8298.75</v>
+        <v>7413.55</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>173.9</v>
+        <v>174</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.27</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -650,24 +650,24 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.92</v>
+        <v>0.915</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9200</v>
+        <v>9150</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>138.34</v>
+        <v>138.33</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>553360</v>
+        <v>553320</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>15480</v>
+        <v>15440</v>
       </c>
     </row>
     <row r="12">
@@ -704,24 +704,24 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.285</v>
+        <v>0.28</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>20000</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="13">
@@ -758,24 +758,24 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
         <v>9412</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>941.2</v>
+        <v>988.26</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>28.24</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="15">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>35.55</v>
+        <v>35.605</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>32.94</v>
+        <v>32.95</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>42426.72</v>
+        <v>42439.6</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1481.2</v>
+        <v>1494.08</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1801016.01</v>
+        <v>1803127.08</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>25930.82</v>
+        <v>28041.89</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260811.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260811.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.622</v>
+        <v>1.6</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.047</v>
+        <v>0.025</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>248459.58</v>
+        <v>245089.6</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>7199.51</v>
+        <v>3829.53</v>
       </c>
     </row>
     <row r="5">
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>163800</v>
+        <v>165900</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-700</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="6">
@@ -542,24 +542,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.19</v>
+        <v>1.185</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.025</v>
+        <v>-0.03</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-2.06%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>57458</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>68375.02</v>
+        <v>68087.73</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1436.45</v>
+        <v>-1723.74</v>
       </c>
     </row>
     <row r="7">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>64.19</v>
+        <v>63.93</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.67</v>
+        <v>0.41</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>710262.35</v>
+        <v>707385.45</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7413.55</v>
+        <v>4536.65</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>174</v>
+        <v>173.92</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.35</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -650,24 +650,24 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.915</v>
+        <v>0.89</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.015</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>-1.66%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9150</v>
+        <v>8900</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>100</v>
+        <v>-150</v>
       </c>
     </row>
     <row r="11">
@@ -758,24 +758,24 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.25%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
         <v>9412</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>988.26</v>
+        <v>941.2</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>75.3</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="15">
@@ -785,24 +785,24 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.1</v>
+        <v>0.099</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
         <v>6000</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="16">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>35.605</v>
+        <v>35.69</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.095</v>
+        <v>-0.01</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>32.95</v>
+        <v>33.01</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>3.84%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>42439.6</v>
+        <v>42516.88</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1494.08</v>
+        <v>1571.36</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1803127.08</v>
+        <v>1798467.13</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>28041.89</v>
+        <v>23381.94</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260811.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260811.xlsx
@@ -596,24 +596,24 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-25.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
         <v>44090</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>132.27</v>
+        <v>176.36</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-44.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -731,24 +731,24 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
         <v>700000</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1798467.13</v>
+        <v>1799911.22</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>23381.94</v>
+        <v>24826.03</v>
       </c>
     </row>
   </sheetData>
